--- a/other-files/student_tools.xlsx
+++ b/other-files/student_tools.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ashle\Documents\GitHub\student-model-gallery\other-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69AE7E68-E3DA-4867-B0F6-BD8D15487980}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42A4FAEC-1033-4D98-B85D-A946A6727713}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-48" yWindow="-48" windowWidth="23136" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Student Tools" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="178">
   <si>
     <t>Initials</t>
   </si>
@@ -524,6 +524,36 @@
   </si>
   <si>
     <t>turf</t>
+  </si>
+  <si>
+    <t>alyami </t>
+  </si>
+  <si>
+    <t>AR</t>
+  </si>
+  <si>
+    <t>aloyana</t>
+  </si>
+  <si>
+    <t>AY</t>
+  </si>
+  <si>
+    <t>yanez</t>
+  </si>
+  <si>
+    <t>SY</t>
+  </si>
+  <si>
+    <t>garrett</t>
+  </si>
+  <si>
+    <t>MG</t>
+  </si>
+  <si>
+    <t>DA</t>
+  </si>
+  <si>
+    <t>domini</t>
   </si>
 </sst>
 </file>
@@ -545,7 +575,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -558,8 +588,14 @@
         <bgColor rgb="FF4472C4"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -582,16 +618,29 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -836,7 +885,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C56"/>
+  <dimension ref="A1:D62"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.81640625" customWidth="1"/>
@@ -844,7 +893,7 @@
     <col min="3" max="3" width="19.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -855,7 +904,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -865,8 +914,9 @@
       <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D2" s="3"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -876,8 +926,9 @@
       <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D3" s="3"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -887,8 +938,9 @@
       <c r="C4" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D4" s="3"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
@@ -899,7 +951,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -909,8 +961,9 @@
       <c r="C6" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D6" s="3"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
@@ -920,8 +973,9 @@
       <c r="C7" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D7" s="3"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>21</v>
       </c>
@@ -932,7 +986,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>24</v>
       </c>
@@ -942,8 +996,9 @@
       <c r="C9" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D9" s="3"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>27</v>
       </c>
@@ -953,8 +1008,9 @@
       <c r="C10" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D10" s="3"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>30</v>
       </c>
@@ -964,8 +1020,9 @@
       <c r="C11" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D11" s="3"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>33</v>
       </c>
@@ -975,8 +1032,9 @@
       <c r="C12" s="1" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D12" s="3"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>36</v>
       </c>
@@ -986,8 +1044,9 @@
       <c r="C13" s="1" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D13" s="3"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>39</v>
       </c>
@@ -997,8 +1056,9 @@
       <c r="C14" s="1" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D14" s="3"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>42</v>
       </c>
@@ -1008,8 +1068,9 @@
       <c r="C15" s="1" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D15" s="3"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>45</v>
       </c>
@@ -1020,7 +1081,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>48</v>
       </c>
@@ -1031,7 +1092,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>51</v>
       </c>
@@ -1042,7 +1103,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>54</v>
       </c>
@@ -1053,7 +1114,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>57</v>
       </c>
@@ -1064,7 +1125,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>60</v>
       </c>
@@ -1075,7 +1136,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>63</v>
       </c>
@@ -1085,8 +1146,9 @@
       <c r="C22" s="1" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D22" s="3"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>66</v>
       </c>
@@ -1097,7 +1159,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>69</v>
       </c>
@@ -1108,7 +1170,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>72</v>
       </c>
@@ -1118,8 +1180,9 @@
       <c r="C25" s="1" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D25" s="3"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>75</v>
       </c>
@@ -1130,7 +1193,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>78</v>
       </c>
@@ -1141,7 +1204,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>81</v>
       </c>
@@ -1152,7 +1215,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>84</v>
       </c>
@@ -1163,7 +1226,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>87</v>
       </c>
@@ -1174,7 +1237,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>90</v>
       </c>
@@ -1185,7 +1248,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>93</v>
       </c>
@@ -1196,7 +1259,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>96</v>
       </c>
@@ -1207,7 +1270,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>99</v>
       </c>
@@ -1218,7 +1281,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>102</v>
       </c>
@@ -1229,7 +1292,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>105</v>
       </c>
@@ -1240,7 +1303,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>108</v>
       </c>
@@ -1251,7 +1314,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>111</v>
       </c>
@@ -1262,7 +1325,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>114</v>
       </c>
@@ -1273,7 +1336,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>117</v>
       </c>
@@ -1284,7 +1347,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>120</v>
       </c>
@@ -1295,7 +1358,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>123</v>
       </c>
@@ -1306,7 +1369,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>126</v>
       </c>
@@ -1317,7 +1380,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>129</v>
       </c>
@@ -1327,8 +1390,9 @@
       <c r="C44" s="1" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D44" s="3"/>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>132</v>
       </c>
@@ -1339,7 +1403,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>135</v>
       </c>
@@ -1350,7 +1414,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>138</v>
       </c>
@@ -1361,7 +1425,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>141</v>
       </c>
@@ -1459,6 +1523,49 @@
       <c r="C56" s="1" t="s">
         <v>167</v>
       </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="C57" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="C58" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="C59" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="C60" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="C61" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/other-files/student_tools.xlsx
+++ b/other-files/student_tools.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ashle\Documents\GitHub\student-model-gallery\other-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42A4FAEC-1033-4D98-B85D-A946A6727713}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEDF51B9-AAA8-4F4E-9163-C5EA9E79A7E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-48" yWindow="-48" windowWidth="23136" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -640,7 +640,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -950,6 +950,7 @@
       <c r="C5" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="D5" s="3"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
@@ -1091,6 +1092,7 @@
       <c r="C17" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="D17" s="3"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
@@ -1169,6 +1171,7 @@
       <c r="C24" s="1" t="s">
         <v>71</v>
       </c>
+      <c r="D24" s="3"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
@@ -1192,6 +1195,7 @@
       <c r="C26" s="1" t="s">
         <v>77</v>
       </c>
+      <c r="D26" s="3"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
@@ -1203,6 +1207,7 @@
       <c r="C27" s="1" t="s">
         <v>80</v>
       </c>
+      <c r="D27" s="3"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
@@ -1214,6 +1219,7 @@
       <c r="C28" s="1" t="s">
         <v>83</v>
       </c>
+      <c r="D28" s="3"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
@@ -1225,6 +1231,7 @@
       <c r="C29" s="1" t="s">
         <v>86</v>
       </c>
+      <c r="D29" s="3"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
@@ -1236,6 +1243,7 @@
       <c r="C30" s="1" t="s">
         <v>89</v>
       </c>
+      <c r="D30" s="3"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
@@ -1247,6 +1255,7 @@
       <c r="C31" s="1" t="s">
         <v>92</v>
       </c>
+      <c r="D31" s="3"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
@@ -1280,6 +1289,7 @@
       <c r="C34" s="1" t="s">
         <v>101</v>
       </c>
+      <c r="D34" s="3"/>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
@@ -1291,6 +1301,7 @@
       <c r="C35" s="1" t="s">
         <v>104</v>
       </c>
+      <c r="D35" s="3"/>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
@@ -1324,6 +1335,7 @@
       <c r="C38" s="1" t="s">
         <v>113</v>
       </c>
+      <c r="D38" s="3"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
@@ -1346,6 +1358,7 @@
       <c r="C40" s="1" t="s">
         <v>119</v>
       </c>
+      <c r="D40" s="3"/>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
@@ -1424,6 +1437,7 @@
       <c r="C47" s="1" t="s">
         <v>140</v>
       </c>
+      <c r="D47" s="3"/>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
@@ -1435,6 +1449,7 @@
       <c r="C48" s="1" t="s">
         <v>143</v>
       </c>
+      <c r="D48" s="3"/>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">

--- a/other-files/student_tools.xlsx
+++ b/other-files/student_tools.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ashle\Documents\GitHub\student-model-gallery\other-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEDF51B9-AAA8-4F4E-9163-C5EA9E79A7E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{265A2E21-052C-4444-A4DD-55E5EE8F0AC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-48" yWindow="-48" windowWidth="23136" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="183">
   <si>
     <t>Initials</t>
   </si>
@@ -554,6 +554,21 @@
   </si>
   <si>
     <t>domini</t>
+  </si>
+  <si>
+    <t>smith</t>
+  </si>
+  <si>
+    <t>BS</t>
+  </si>
+  <si>
+    <t>tripp</t>
+  </si>
+  <si>
+    <t>TA</t>
+  </si>
+  <si>
+    <t>https://gemini.google.com/share/882baa87882c</t>
   </si>
 </sst>
 </file>
@@ -575,7 +590,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -591,6 +606,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -633,7 +654,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -641,6 +662,8 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -885,7 +908,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D62"/>
+  <dimension ref="A1:D63"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.81640625" customWidth="1"/>
@@ -986,6 +1009,7 @@
       <c r="C8" s="1" t="s">
         <v>23</v>
       </c>
+      <c r="D8" s="6"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
@@ -1081,6 +1105,7 @@
       <c r="C16" s="1" t="s">
         <v>47</v>
       </c>
+      <c r="D16" s="3"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
@@ -1104,6 +1129,7 @@
       <c r="C18" s="1" t="s">
         <v>53</v>
       </c>
+      <c r="D18" s="3"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
@@ -1115,6 +1141,7 @@
       <c r="C19" s="1" t="s">
         <v>56</v>
       </c>
+      <c r="D19" s="3"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
@@ -1126,6 +1153,7 @@
       <c r="C20" s="1" t="s">
         <v>59</v>
       </c>
+      <c r="D20" s="3"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
@@ -1137,6 +1165,7 @@
       <c r="C21" s="1" t="s">
         <v>62</v>
       </c>
+      <c r="D21" s="3"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
@@ -1160,6 +1189,7 @@
       <c r="C23" s="1" t="s">
         <v>68</v>
       </c>
+      <c r="D23" s="6"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
@@ -1267,6 +1297,7 @@
       <c r="C32" s="1" t="s">
         <v>95</v>
       </c>
+      <c r="D32" s="3"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
@@ -1278,6 +1309,7 @@
       <c r="C33" s="1" t="s">
         <v>98</v>
       </c>
+      <c r="D33" s="3"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
@@ -1313,6 +1345,7 @@
       <c r="C36" s="1" t="s">
         <v>107</v>
       </c>
+      <c r="D36" s="3"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
@@ -1324,6 +1357,7 @@
       <c r="C37" s="1" t="s">
         <v>110</v>
       </c>
+      <c r="D37" s="3"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
@@ -1347,6 +1381,7 @@
       <c r="C39" s="1" t="s">
         <v>116</v>
       </c>
+      <c r="D39" s="3"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
@@ -1370,6 +1405,7 @@
       <c r="C41" s="1" t="s">
         <v>122</v>
       </c>
+      <c r="D41" s="3"/>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
@@ -1381,6 +1417,7 @@
       <c r="C42" s="1" t="s">
         <v>125</v>
       </c>
+      <c r="D42" s="3"/>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
@@ -1392,6 +1429,7 @@
       <c r="C43" s="1" t="s">
         <v>128</v>
       </c>
+      <c r="D43" s="3"/>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
@@ -1415,6 +1453,7 @@
       <c r="C45" s="1" t="s">
         <v>134</v>
       </c>
+      <c r="D45" s="3"/>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
@@ -1426,6 +1465,7 @@
       <c r="C46" s="1" t="s">
         <v>137</v>
       </c>
+      <c r="D46" s="3"/>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
@@ -1451,7 +1491,7 @@
       </c>
       <c r="D48" s="3"/>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>144</v>
       </c>
@@ -1461,8 +1501,9 @@
       <c r="C49" s="1" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D49" s="3"/>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>147</v>
       </c>
@@ -1472,8 +1513,9 @@
       <c r="C50" s="1" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D50" s="3"/>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>150</v>
       </c>
@@ -1483,8 +1525,9 @@
       <c r="C51" s="1" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D51" s="6"/>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>153</v>
       </c>
@@ -1494,8 +1537,9 @@
       <c r="C52" s="1" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D52" s="3"/>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>156</v>
       </c>
@@ -1505,8 +1549,9 @@
       <c r="C53" s="1" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D53" s="3"/>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>159</v>
       </c>
@@ -1516,8 +1561,9 @@
       <c r="C54" s="1" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D54" s="3"/>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>162</v>
       </c>
@@ -1527,8 +1573,9 @@
       <c r="C55" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D55" s="3"/>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>165</v>
       </c>
@@ -1538,8 +1585,9 @@
       <c r="C56" s="1" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D56" s="3"/>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
         <v>169</v>
       </c>
@@ -1547,7 +1595,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
         <v>171</v>
       </c>
@@ -1555,7 +1603,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
         <v>173</v>
       </c>
@@ -1563,7 +1611,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="s">
         <v>175</v>
       </c>
@@ -1571,7 +1619,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
         <v>176</v>
       </c>
@@ -1579,8 +1627,24 @@
         <v>177</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A62" s="4"/>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A62" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="C62" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A63" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="C63" t="s">
+        <v>180</v>
+      </c>
+      <c r="D63" t="s">
+        <v>182</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/other-files/student_tools.xlsx
+++ b/other-files/student_tools.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ashle\Documents\GitHub\student-model-gallery\other-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{265A2E21-052C-4444-A4DD-55E5EE8F0AC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A655D72-F6CC-44AB-B661-3F84AFAC1A9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-48" yWindow="-48" windowWidth="23136" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="190">
   <si>
     <t>Initials</t>
   </si>
@@ -568,7 +568,28 @@
     <t>TA</t>
   </si>
   <si>
-    <t>https://gemini.google.com/share/882baa87882c</t>
+    <t>Mochi Gumdrop</t>
+  </si>
+  <si>
+    <t>Taffy Apricot</t>
+  </si>
+  <si>
+    <t>Brownie Sundae</t>
+  </si>
+  <si>
+    <t>Dusk Andromeda</t>
+  </si>
+  <si>
+    <t>Starlight Yew</t>
+  </si>
+  <si>
+    <t>Almond Yuzu</t>
+  </si>
+  <si>
+    <t>Amber Rosehip</t>
+  </si>
+  <si>
+    <t>Tool 2?</t>
   </si>
 </sst>
 </file>
@@ -588,9 +609,10 @@
       <sz val="12"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -615,8 +637,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -639,17 +673,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -661,9 +684,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -926,6 +949,9 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
+      <c r="D1" s="6" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -1009,7 +1035,7 @@
       <c r="C8" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="6"/>
+      <c r="D8" s="4"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
@@ -1189,7 +1215,7 @@
       <c r="C23" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D23" s="6"/>
+      <c r="D23" s="4"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
@@ -1525,7 +1551,7 @@
       <c r="C51" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="D51" s="6"/>
+      <c r="D51" s="3"/>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
@@ -1588,65 +1614,91 @@
       <c r="D56" s="3"/>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A57" s="4" t="s">
+      <c r="A57" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="C57" t="s">
+      <c r="B57" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="C57" s="1" t="s">
         <v>168</v>
       </c>
+      <c r="D57" s="3"/>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A58" s="4" t="s">
+      <c r="A58" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="C58" t="s">
+      <c r="B58" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C58" s="1" t="s">
         <v>170</v>
       </c>
+      <c r="D58" s="3"/>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A59" s="4" t="s">
+      <c r="A59" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="C59" t="s">
+      <c r="B59" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C59" s="1" t="s">
         <v>172</v>
       </c>
+      <c r="D59" s="5"/>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A60" s="4" t="s">
+      <c r="A60" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="C60" t="s">
+      <c r="B60" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C60" s="1" t="s">
         <v>174</v>
       </c>
+      <c r="D60" s="3"/>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A61" s="4" t="s">
+      <c r="A61" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="C61" t="s">
+      <c r="B61" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C61" s="1" t="s">
         <v>177</v>
       </c>
+      <c r="D61" s="5"/>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A62" s="4" t="s">
+      <c r="A62" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="C62" t="s">
+      <c r="B62" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C62" s="1" t="s">
         <v>178</v>
       </c>
+      <c r="D62" s="3"/>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A63" s="5" t="s">
+      <c r="A63" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="C63" t="s">
+      <c r="B63" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C63" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="D63" t="s">
-        <v>182</v>
-      </c>
+      <c r="D63" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>